--- a/public/templates/template_instansi.xlsx
+++ b/public/templates/template_instansi.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="17">
   <si>
     <t>nama_instansi</t>
   </si>
@@ -50,10 +50,10 @@
     <t>Bpk. M.Tafirhan</t>
   </si>
   <si>
-    <t>KETERANGAN:</t>
-  </si>
-  <si>
-    <t>- nama_instansi: Wajib, max 50 karakter</t>
+    <t>BACA KETERANGAN!!! :</t>
+  </si>
+  <si>
+    <t>- nama_instansi: Wajib, max 255 karakter</t>
   </si>
   <si>
     <t>- Auto create Mentor (password: @mentor123)</t>
@@ -62,7 +62,10 @@
     <t>- Hapus baris 2 sebelum import!</t>
   </si>
   <si>
-    <t>- Disarankan menggunakan spreadsheet dibanding excel</t>
+    <t>- Disarankan menggunakan SPREADSHEET</t>
+  </si>
+  <si>
+    <t>- !!!(FORMAT SEMUA COLUMN MENJADI TEKS BIASA)</t>
   </si>
 </sst>
 </file>
@@ -430,7 +433,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="true" style="0"/>
@@ -511,6 +514,11 @@
     <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
